--- a/DRAGO/Mayo/EXPENSAS-MAYO.xlsx
+++ b/DRAGO/Mayo/EXPENSAS-MAYO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\DRAGO\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA56C41-866F-45DF-B4ED-822FDEBEFA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB57DC2-60F1-4920-99FA-14706E88295D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1052,6 +1052,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="3" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1099,9 +1102,6 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -50355,8 +50355,8 @@
       <c r="B20" s="90" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="85">
-        <v>13201.74</v>
+      <c r="C20" s="101">
+        <v>13432.94</v>
       </c>
       <c r="D20" s="5"/>
       <c r="E20" s="14"/>
@@ -50369,7 +50369,7 @@
       <c r="B21" s="90" t="s">
         <v>78</v>
       </c>
-      <c r="C21" s="136">
+      <c r="C21" s="120">
         <v>155247.07999999999</v>
       </c>
       <c r="D21" s="49"/>
@@ -50396,7 +50396,7 @@
       <c r="B23" s="92"/>
       <c r="C23" s="64">
         <f>SUM(C17:C22)</f>
-        <v>249757.19999999998</v>
+        <v>249988.4</v>
       </c>
     </row>
     <row r="24" spans="1:16384" customFormat="1" x14ac:dyDescent="0.3">
@@ -50467,7 +50467,7 @@
       <c r="B31" s="80"/>
       <c r="C31" s="95">
         <f>+C30+C23</f>
-        <v>344961.14999999997</v>
+        <v>345192.35</v>
       </c>
       <c r="F31" s="22"/>
     </row>
@@ -50522,7 +50522,7 @@
       <c r="B40" s="35"/>
       <c r="C40" s="36">
         <f>+C38+C31</f>
-        <v>344961.14999999997</v>
+        <v>345192.35</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -50566,7 +50566,7 @@
       </c>
       <c r="C46" s="96">
         <f>-(C31-C29)</f>
-        <v>-344961.14999999997</v>
+        <v>-345192.35</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -50576,7 +50576,7 @@
       <c r="B47" s="34"/>
       <c r="C47" s="41">
         <f>SUM(C43:C46)</f>
-        <v>284403.27692240005</v>
+        <v>284172.07692240004</v>
       </c>
       <c r="D47" s="6"/>
     </row>
@@ -50707,58 +50707,58 @@
       <c r="M2" s="105"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="122"/>
-      <c r="B3" s="120" t="s">
+      <c r="A3" s="123"/>
+      <c r="B3" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="128" t="s">
+      <c r="C3" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="129" t="s">
+      <c r="D3" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="120" t="s">
+      <c r="E3" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="126" t="s">
+      <c r="F3" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="128" t="s">
+      <c r="G3" s="129" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="126" t="s">
+      <c r="H3" s="127" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="128" t="s">
+      <c r="I3" s="129" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="130" t="s">
+      <c r="J3" s="131" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="124" t="s">
+      <c r="K3" s="125" t="s">
         <v>85</v>
       </c>
-      <c r="L3" s="124" t="s">
+      <c r="L3" s="125" t="s">
         <v>86</v>
       </c>
-      <c r="M3" s="124" t="s">
+      <c r="M3" s="125" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="123"/>
-      <c r="B4" s="121"/>
-      <c r="C4" s="128"/>
-      <c r="D4" s="129"/>
-      <c r="E4" s="121"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="128"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="128"/>
-      <c r="J4" s="130"/>
-      <c r="K4" s="125"/>
-      <c r="L4" s="125"/>
-      <c r="M4" s="125"/>
+      <c r="A4" s="124"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="126"/>
+      <c r="M4" s="126"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="106">
@@ -51601,11 +51601,11 @@
       <c r="D1" s="58">
         <v>50000</v>
       </c>
-      <c r="H1" s="135">
+      <c r="H1" s="136">
         <v>250000</v>
       </c>
-      <c r="I1" s="135"/>
-      <c r="J1" s="135"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="55" t="s">
@@ -51669,13 +51669,13 @@
         <v>58</v>
       </c>
       <c r="K4" s="71"/>
-      <c r="L4" s="133" t="s">
+      <c r="L4" s="134" t="s">
         <v>74</v>
       </c>
       <c r="M4" s="82" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="131" t="s">
+      <c r="N4" s="132" t="s">
         <v>59</v>
       </c>
       <c r="P4" s="21"/>
@@ -51704,11 +51704,11 @@
         <v>73</v>
       </c>
       <c r="K5" s="61"/>
-      <c r="L5" s="134"/>
+      <c r="L5" s="135"/>
       <c r="M5" s="83" t="s">
         <v>75</v>
       </c>
-      <c r="N5" s="132"/>
+      <c r="N5" s="133"/>
       <c r="P5" s="21"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">

--- a/DRAGO/Mayo/EXPENSAS-MAYO.xlsx
+++ b/DRAGO/Mayo/EXPENSAS-MAYO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\DRAGO\Mayo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5152D3-B35B-41C3-A960-783DC34C7BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB698AE-831E-46A6-A200-50F8C3D2A168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>UF</t>
   </si>
@@ -299,13 +299,17 @@
   </si>
   <si>
     <t>Vto. 16/06</t>
+  </si>
+  <si>
+    <t>enzo habia pagado todo y lo pusimos con deuda</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
@@ -442,7 +446,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -479,6 +483,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="31">
     <border>
@@ -1045,6 +1055,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="1" fillId="3" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="1" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1093,15 +1108,8 @@
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1469,7 +1477,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H57"/>
+  <dimension ref="A2:H54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1563,58 +1571,58 @@
       <c r="B17" s="87" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="134">
+      <c r="C17" s="118">
         <v>37561.17</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="14"/>
     </row>
-    <row r="18" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="77" t="s">
         <v>71</v>
       </c>
       <c r="B18" s="88"/>
-      <c r="C18" s="134">
+      <c r="C18" s="118">
         <v>3567.21</v>
       </c>
       <c r="D18" s="49"/>
       <c r="E18" s="14"/>
     </row>
-    <row r="19" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="77" t="s">
         <v>46</v>
       </c>
       <c r="B19" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="C19" s="134">
+      <c r="C19" s="118">
         <v>13432.94</v>
       </c>
       <c r="D19" s="5"/>
       <c r="E19" s="14"/>
       <c r="F19" s="18"/>
     </row>
-    <row r="20" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="77" t="s">
         <v>35</v>
       </c>
       <c r="B20" s="89" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="135">
+      <c r="C20" s="119">
         <v>155247.07999999999</v>
       </c>
       <c r="D20" s="49"/>
       <c r="F20" s="14"/>
     </row>
-    <row r="21" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="77" t="s">
         <v>36</v>
       </c>
       <c r="B21" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="134">
+      <c r="C21" s="118">
         <v>40180</v>
       </c>
       <c r="D21" s="5"/>
@@ -1623,41 +1631,41 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="90"/>
       <c r="B22" s="91"/>
-      <c r="C22" s="136">
+      <c r="C22" s="120">
         <f>SUM(C17:C21)</f>
         <v>249988.4</v>
       </c>
     </row>
-    <row r="23" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="86" t="s">
         <v>37</v>
       </c>
       <c r="B23" s="89"/>
-      <c r="C23" s="137"/>
-    </row>
-    <row r="24" spans="1:8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C23" s="11"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="77" t="s">
         <v>72</v>
       </c>
       <c r="B24" s="92" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="134">
+      <c r="C24" s="118">
         <f>65200+65200*5%</f>
         <v>68460</v>
       </c>
       <c r="F24" s="22"/>
     </row>
-    <row r="25" spans="1:8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="77"/>
       <c r="B25" s="92"/>
       <c r="C25" s="99"/>
       <c r="F25" s="22"/>
     </row>
-    <row r="26" spans="1:8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="77" t="s">
         <v>83</v>
       </c>
@@ -1667,7 +1675,7 @@
       <c r="E26" s="14"/>
       <c r="F26" s="22"/>
     </row>
-    <row r="27" spans="1:8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="90"/>
       <c r="B27" s="91"/>
       <c r="C27" s="64">
@@ -1676,7 +1684,7 @@
       </c>
       <c r="F27" s="22"/>
     </row>
-    <row r="28" spans="1:8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="80" t="s">
         <v>82</v>
       </c>
@@ -1687,40 +1695,40 @@
       </c>
       <c r="F28" s="22"/>
     </row>
-    <row r="29" spans="1:8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C29" s="65"/>
       <c r="F29" s="22"/>
     </row>
-    <row r="30" spans="1:8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="23" t="s">
         <v>47</v>
       </c>
       <c r="C30" s="65"/>
       <c r="F30" s="22"/>
     </row>
-    <row r="31" spans="1:8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="77"/>
       <c r="B31" s="77"/>
       <c r="C31" s="84"/>
       <c r="F31" s="22"/>
     </row>
-    <row r="32" spans="1:8" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="77"/>
       <c r="B32" s="77"/>
       <c r="C32" s="85"/>
       <c r="F32" s="22"/>
     </row>
-    <row r="33" spans="1:6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="77"/>
       <c r="B33" s="77"/>
       <c r="C33" s="85"/>
       <c r="F33" s="22"/>
     </row>
-    <row r="34" spans="1:6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C34" s="67"/>
       <c r="F34" s="22"/>
     </row>
-    <row r="35" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="23" t="s">
         <v>43</v>
       </c>
@@ -1731,7 +1739,7 @@
       </c>
       <c r="E35" s="14"/>
     </row>
-    <row r="37" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="35" t="s">
         <v>15</v>
       </c>
@@ -1741,12 +1749,12 @@
         <v>318448.40000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="40" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="37" t="s">
         <v>10</v>
       </c>
@@ -1757,7 +1765,7 @@
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
     </row>
-    <row r="41" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>9</v>
       </c>
@@ -1768,7 +1776,7 @@
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
     </row>
-    <row r="42" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>80</v>
       </c>
@@ -1776,7 +1784,7 @@
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
     </row>
-    <row r="43" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>79</v>
       </c>
@@ -1785,7 +1793,7 @@
         <v>-318448.40000000002</v>
       </c>
     </row>
-    <row r="44" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="37" t="s">
         <v>16</v>
       </c>
@@ -1796,23 +1804,23 @@
       </c>
       <c r="D44" s="6"/>
     </row>
-    <row r="45" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="19"/>
       <c r="B45" s="18"/>
       <c r="C45" s="20"/>
     </row>
-    <row r="46" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="19"/>
       <c r="B46" s="18"/>
       <c r="C46" s="20"/>
       <c r="F46" s="95"/>
     </row>
-    <row r="47" spans="1:6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="19"/>
       <c r="B47" s="18"/>
       <c r="C47" s="20"/>
     </row>
-    <row r="48" spans="1:6" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="76" t="s">
         <v>69</v>
       </c>
@@ -1821,12 +1829,12 @@
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="49" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="77"/>
       <c r="B49" s="77"/>
       <c r="C49" s="83"/>
     </row>
-    <row r="50" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="80" t="s">
         <v>4</v>
       </c>
@@ -1836,29 +1844,26 @@
         <v>109834.99657000002</v>
       </c>
     </row>
-    <row r="51" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="18"/>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
     </row>
-    <row r="52" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="18"/>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
     </row>
-    <row r="53" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="18"/>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
     </row>
-    <row r="54" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="18"/>
       <c r="B54" s="18"/>
       <c r="C54" s="18"/>
     </row>
-    <row r="55" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:3" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -1875,7 +1880,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
@@ -1893,7 +1898,7 @@
     <col min="15" max="15" width="11.42578125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="55" t="s">
         <v>52</v>
       </c>
@@ -1905,7 +1910,7 @@
         <v>Vto. 16/06</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="107" t="str">
         <f>'detalle y gastos'!B7</f>
         <v>LIQUIDACIÓN EXPENSAS MAYO 2025</v>
@@ -1925,61 +1930,61 @@
       <c r="L2" s="102"/>
       <c r="M2" s="103"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="120"/>
-      <c r="B3" s="118" t="s">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="123"/>
+      <c r="B3" s="121" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="126" t="s">
+      <c r="C3" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="127" t="s">
+      <c r="D3" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="118" t="s">
+      <c r="E3" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="124" t="s">
+      <c r="F3" s="127" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="126" t="s">
+      <c r="G3" s="129" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="124" t="s">
+      <c r="H3" s="127" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="126" t="s">
+      <c r="I3" s="129" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="128" t="s">
+      <c r="J3" s="131" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="122" t="s">
+      <c r="K3" s="125" t="s">
         <v>85</v>
       </c>
-      <c r="L3" s="122" t="s">
+      <c r="L3" s="125" t="s">
         <v>86</v>
       </c>
-      <c r="M3" s="122" t="s">
+      <c r="M3" s="125" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="121"/>
-      <c r="B4" s="119"/>
-      <c r="C4" s="126"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="119"/>
-      <c r="F4" s="125"/>
-      <c r="G4" s="126"/>
-      <c r="H4" s="125"/>
-      <c r="I4" s="126"/>
-      <c r="J4" s="128"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="123"/>
-      <c r="M4" s="123"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="124"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="129"/>
+      <c r="D4" s="130"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="128"/>
+      <c r="G4" s="129"/>
+      <c r="H4" s="128"/>
+      <c r="I4" s="129"/>
+      <c r="J4" s="131"/>
+      <c r="K4" s="126"/>
+      <c r="L4" s="126"/>
+      <c r="M4" s="126"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="104">
         <v>1</v>
       </c>
@@ -1995,7 +2000,7 @@
       <c r="E5" s="47">
         <v>40540.144919999999</v>
       </c>
-      <c r="F5" s="138">
+      <c r="F5" s="47">
         <f>E5</f>
         <v>40540.144919999999</v>
       </c>
@@ -2024,7 +2029,7 @@
         <v>40073.546655999999</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="104">
         <v>2</v>
       </c>
@@ -2040,7 +2045,7 @@
       <c r="E6" s="47">
         <v>39673.982020000003</v>
       </c>
-      <c r="F6" s="138">
+      <c r="F6" s="47">
         <v>31231.37</v>
       </c>
       <c r="G6" s="47">
@@ -2067,8 +2072,12 @@
         <f t="shared" ref="M6:M12" si="3">L6+L6*4%</f>
         <v>49624.065317840003</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="O6" s="138" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q6" s="137"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="104">
         <v>3</v>
       </c>
@@ -2082,7 +2091,7 @@
       <c r="E7" s="47">
         <v>39199.974840000003</v>
       </c>
-      <c r="F7" s="138">
+      <c r="F7" s="47">
         <f>E7</f>
         <v>39199.974840000003</v>
       </c>
@@ -2111,7 +2120,7 @@
         <v>38748.801312000011</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="104">
         <v>4</v>
       </c>
@@ -2127,7 +2136,7 @@
       <c r="E8" s="47">
         <v>122096.58983218967</v>
       </c>
-      <c r="F8" s="138"/>
+      <c r="F8" s="47"/>
       <c r="G8" s="47">
         <f t="shared" si="0"/>
         <v>122096.58983218967</v>
@@ -2153,7 +2162,7 @@
         <v>172078.27740875114</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="104">
         <v>5</v>
       </c>
@@ -2169,7 +2178,7 @@
       <c r="E9" s="47">
         <v>45900.825240000006</v>
       </c>
-      <c r="F9" s="138">
+      <c r="F9" s="47">
         <f t="shared" ref="F9" si="4">E9</f>
         <v>45900.825240000006</v>
       </c>
@@ -2198,7 +2207,7 @@
         <v>45372.528032000009</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="104">
         <v>6</v>
       </c>
@@ -2214,7 +2223,7 @@
       <c r="E10" s="47">
         <v>42955.266120000015</v>
       </c>
-      <c r="F10" s="138">
+      <c r="F10" s="47">
         <f>E10</f>
         <v>42955.266120000015</v>
       </c>
@@ -2243,7 +2252,7 @@
         <v>43716.596352</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="104">
         <v>7</v>
       </c>
@@ -2259,7 +2268,7 @@
       <c r="E11" s="47">
         <v>42550.40004</v>
       </c>
-      <c r="F11" s="138">
+      <c r="F11" s="47">
         <f>E11</f>
         <v>42550.40004</v>
       </c>
@@ -2288,7 +2297,7 @@
         <v>42060.664672000006</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="104">
         <v>8</v>
       </c>
@@ -2304,7 +2313,7 @@
       <c r="E12" s="47">
         <v>42550.40004</v>
       </c>
-      <c r="F12" s="138">
+      <c r="F12" s="47">
         <f>E12</f>
         <v>42550.40004</v>
       </c>
@@ -2333,7 +2342,7 @@
         <v>42060.664672000006</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="113" t="s">
         <v>11</v>
       </c>
@@ -2374,7 +2383,7 @@
         <v>473735.14442259114</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="55" t="s">
         <v>53</v>
       </c>
@@ -2822,11 +2831,11 @@
       <c r="D1" s="58">
         <v>50000</v>
       </c>
-      <c r="H1" s="133">
+      <c r="H1" s="136">
         <v>250000</v>
       </c>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="55" t="s">
@@ -2890,13 +2899,13 @@
         <v>58</v>
       </c>
       <c r="K4" s="71"/>
-      <c r="L4" s="131" t="s">
+      <c r="L4" s="134" t="s">
         <v>74</v>
       </c>
       <c r="M4" s="81" t="s">
         <v>5</v>
       </c>
-      <c r="N4" s="129" t="s">
+      <c r="N4" s="132" t="s">
         <v>59</v>
       </c>
       <c r="P4" s="21"/>
@@ -2925,11 +2934,11 @@
         <v>73</v>
       </c>
       <c r="K5" s="61"/>
-      <c r="L5" s="132"/>
+      <c r="L5" s="135"/>
       <c r="M5" s="82" t="s">
         <v>75</v>
       </c>
-      <c r="N5" s="130"/>
+      <c r="N5" s="133"/>
       <c r="P5" s="21"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
